--- a/data/trans_camb/P16A06-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A06-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,37</t>
+          <t>-1,53; 3,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,41</t>
+          <t>-1,59; 3,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,07</t>
+          <t>-0,52; 4,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 7,04</t>
+          <t>-0,11; 6,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 10,7</t>
+          <t>2,43; 10,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 7,01</t>
+          <t>1,19; 6,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,14</t>
+          <t>-0,06; 4,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,24</t>
+          <t>1,43; 6,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,82</t>
+          <t>1,05; 4,98</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-77,37; 722,77</t>
+          <t>-82,54; 692,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,39; 620,84</t>
+          <t>-78,01; 531,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 732,7</t>
+          <t>-42,81; 699,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 550,68</t>
+          <t>-13,65; 663,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,64; 981,94</t>
+          <t>42,84; 902,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,55; 630,96</t>
+          <t>11,34; 553,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 338,88</t>
+          <t>-6,23; 365,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,65; 495,66</t>
+          <t>34,0; 545,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,22; 396,02</t>
+          <t>21,86; 436,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,4</t>
+          <t>-0,79; 3,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 3,11</t>
+          <t>-0,26; 3,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,1</t>
+          <t>1,36; 5,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 5,19</t>
+          <t>-1,07; 5,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 4,65</t>
+          <t>-1,67; 4,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,4</t>
+          <t>2,34; 8,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,48</t>
+          <t>-0,37; 3,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,41</t>
+          <t>-0,39; 3,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,57</t>
+          <t>2,64; 6,52</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,74; 418,29</t>
+          <t>-49,67; 477,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-33,85; 398,42</t>
+          <t>-26,42; 446,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66,5; 842,36</t>
+          <t>34,25; 772,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,63; 112,9</t>
+          <t>-16,81; 122,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,91; 106,81</t>
+          <t>-25,41; 96,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,23; 194,08</t>
+          <t>31,31; 199,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 126,17</t>
+          <t>-9,1; 125,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 122,05</t>
+          <t>-11,55; 128,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58,67; 237,45</t>
+          <t>54,78; 234,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 3,13</t>
+          <t>0,08; 3,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,93</t>
+          <t>-0,28; 2,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 8,4</t>
+          <t>3,41; 8,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 3,51</t>
+          <t>-0,27; 3,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,49</t>
+          <t>1,49; 6,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,24; 12,87</t>
+          <t>7,34; 12,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,77</t>
+          <t>0,32; 2,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,73</t>
+          <t>0,82; 3,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 10,05</t>
+          <t>6,13; 9,64</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,86; 1306,77</t>
+          <t>-48,1; 1295,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>46,47; 2477,2</t>
+          <t>40,77; 1835,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>253,49; 4013,13</t>
+          <t>334,21; 4033,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 1197,88</t>
+          <t>2,34; 1401,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50,27; 1583,5</t>
+          <t>40,2; 1865,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>422,58; 4929,41</t>
+          <t>493,39; 5638,93</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,62</t>
+          <t>-1,38; 2,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,25</t>
+          <t>-0,77; 2,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,52</t>
+          <t>2,09; 8,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 7,66</t>
+          <t>1,52; 7,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,25; 10,05</t>
+          <t>2,92; 10,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 7,97</t>
+          <t>0,8; 8,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,37</t>
+          <t>0,8; 4,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,17</t>
+          <t>1,71; 6,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,33</t>
+          <t>2,25; 7,18</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-65,47; 676,69</t>
+          <t>-63,62; 508,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-51,14; 625,32</t>
+          <t>-56,52; 751,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53,69; 1506,46</t>
+          <t>59,13; 1618,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22,49; 416,17</t>
+          <t>25,38; 420,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>65,87; 540,83</t>
+          <t>59,26; 618,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,28; 399,1</t>
+          <t>17,67; 386,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,41; 314,51</t>
+          <t>19,76; 309,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>55,33; 411,13</t>
+          <t>54,19; 423,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>79,65; 504,56</t>
+          <t>75,95; 471,58</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 3,55</t>
+          <t>-2,15; 3,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 5,27</t>
+          <t>-1,72; 5,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 4,35</t>
+          <t>-1,46; 4,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,85; 18,63</t>
+          <t>6,46; 18,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 8,69</t>
+          <t>-2,16; 8,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 9,09</t>
+          <t>0,48; 9,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,06; 9,84</t>
+          <t>2,82; 9,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 5,25</t>
+          <t>-0,53; 5,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,8; 6,01</t>
+          <t>1,03; 6,1</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-77,71; 403,56</t>
+          <t>-74,34; 482,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-64,13; 603,6</t>
+          <t>-61,31; 496,09</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-40,51; 541,21</t>
+          <t>-47,75; 494,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>67,64; 547,46</t>
+          <t>67,23; 556,16</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-23,27; 252,75</t>
+          <t>-29,33; 254,04</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,43; 288,49</t>
+          <t>3,52; 284,3</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,11; 359,66</t>
+          <t>44,83; 379,05</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 193,87</t>
+          <t>-13,09; 192,76</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>10,81; 246,64</t>
+          <t>16,22; 239,55</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,12</t>
+          <t>-2,21; 1,05</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,76</t>
+          <t>0,38; 5,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5,22; 10,98</t>
+          <t>5,11; 11,14</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 4,38</t>
+          <t>-1,67; 4,36</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,07; 13,08</t>
+          <t>5,01; 13,44</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,4; 17,51</t>
+          <t>10,07; 17,93</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,15</t>
+          <t>-1,44; 2,16</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,45</t>
+          <t>3,17; 8,43</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8,62; 13,33</t>
+          <t>8,58; 13,24</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-6,08; —</t>
+          <t>-17,52; 1461,33</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>187,19; 2902,63</t>
+          <t>178,29; 3135,84</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-60,1; 314,6</t>
+          <t>-53,38; 356,35</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>83,38; 961,72</t>
+          <t>117,64; 1172,63</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>209,02; 1318,18</t>
+          <t>215,75; 1465,13</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-53,58; 208,2</t>
+          <t>-59,86; 193,76</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>106,18; 774,65</t>
+          <t>100,18; 770,42</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>274,57; 1237,57</t>
+          <t>266,52; 1368,0</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,5</t>
+          <t>-2,38; 0,64</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,03</t>
+          <t>0,84; 4,99</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,3</t>
+          <t>1,35; 5,97</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,59</t>
+          <t>-3,2; 0,86</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,83; 7,17</t>
+          <t>1,93; 7,44</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 9,62</t>
+          <t>0,55; 9,89</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,17</t>
+          <t>-2,32; 0,16</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,6</t>
+          <t>2,1; 5,59</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,92</t>
+          <t>1,97; 7,09</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-77,84; 56,42</t>
+          <t>-80,3; 56,05</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>23,25; 393,02</t>
+          <t>18,19; 374,21</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>45,08; 502,4</t>
+          <t>41,87; 490,49</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-67,85; 22,42</t>
+          <t>-63,8; 34,74</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>34,74; 251,85</t>
+          <t>40,09; 262,96</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,15; 315,82</t>
+          <t>15,19; 321,61</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-59,91; 12,06</t>
+          <t>-63,54; 6,48</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>53,36; 238,3</t>
+          <t>50,16; 238,26</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>54,25; 288,94</t>
+          <t>59,2; 297,59</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,93</t>
+          <t>-2,84; 1,15</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,5; -1,33</t>
+          <t>-4,48; -1,38</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,06</t>
+          <t>-3,49; 0,95</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 3,95</t>
+          <t>-0,95; 4,59</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 1,97</t>
+          <t>-3,4; 1,91</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,31; 5,6</t>
+          <t>-0,01; 5,38</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,01</t>
+          <t>-1,2; 2,03</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,23; -0,16</t>
+          <t>-3,2; -0,15</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,46</t>
+          <t>-2,38; 2,3</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-54,31; 35,1</t>
+          <t>-57,29; 43,19</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-88,32; -37,73</t>
+          <t>-88,58; -41,1</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-68,92; 30,37</t>
+          <t>-69,78; 28,43</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 79,8</t>
+          <t>-12,86; 93,5</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-41,81; 40,62</t>
+          <t>-43,52; 39,52</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,55; 117,25</t>
+          <t>-2,46; 103,68</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 47,36</t>
+          <t>-20,12; 47,92</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-55,29; -1,91</t>
+          <t>-54,42; -3,83</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 53,86</t>
+          <t>-40,04; 52,85</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,78</t>
+          <t>-0,62; 0,74</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,4</t>
+          <t>-0,13; 1,41</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,78</t>
+          <t>1,63; 3,78</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,18</t>
+          <t>1,11; 3,25</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,4</t>
+          <t>2,26; 4,51</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,04</t>
+          <t>3,72; 6,93</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,78</t>
+          <t>0,47; 1,79</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,83</t>
+          <t>1,39; 2,75</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,13</t>
+          <t>3,13; 5,08</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 44,9</t>
+          <t>-27,0; 47,12</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 86,63</t>
+          <t>-5,36; 82,98</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>79,08; 229,36</t>
+          <t>70,91; 227,68</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>23,92; 85,08</t>
+          <t>23,87; 87,31</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>45,74; 117,74</t>
+          <t>48,25; 119,9</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>89,77; 192,54</t>
+          <t>85,29; 189,49</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>13,93; 65,96</t>
+          <t>14,49; 63,92</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>40,08; 100,38</t>
+          <t>40,5; 99,83</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>99,65; 185,41</t>
+          <t>97,33; 179,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A06-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A06-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,89</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,23</t>
+          <t>3,67</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,01</t>
+          <t>2,92</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,23</t>
+          <t>-1,42; 3,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 3,22</t>
+          <t>-1,83; 3,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 4,15</t>
+          <t>-0,33; 4,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 6,86</t>
+          <t>-0,08; 7,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 10,74</t>
+          <t>2,7; 11,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,82</t>
+          <t>0,49; 6,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,08</t>
+          <t>-0,19; 4,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 6,23</t>
+          <t>1,18; 6,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,98</t>
+          <t>1,16; 4,72</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>124,3%</t>
+          <t>142,03%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>167,37%</t>
+          <t>145,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>149,6%</t>
+          <t>145,06%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-82,54; 692,68</t>
+          <t>-72,9; 469,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-78,01; 531,91</t>
+          <t>-78,35; 586,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,81; 699,06</t>
+          <t>-34,01; 671,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 663,48</t>
+          <t>-26,11; 470,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,84; 902,58</t>
+          <t>49,9; 824,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,34; 553,98</t>
+          <t>7,89; 583,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 365,43</t>
+          <t>-12,28; 336,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,0; 545,2</t>
+          <t>34,24; 459,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,86; 436,8</t>
+          <t>30,07; 450,1</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>3,75</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,55</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>4,52</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,37</t>
+          <t>-0,56; 3,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,2</t>
+          <t>-0,26; 3,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,97</t>
+          <t>1,76; 6,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 5,48</t>
+          <t>-1,2; 5,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 4,36</t>
+          <t>-1,95; 4,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 8,47</t>
+          <t>2,21; 8,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 3,46</t>
+          <t>-0,33; 3,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 3,29</t>
+          <t>-0,53; 3,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,52</t>
+          <t>2,7; 6,46</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>252,67%</t>
+          <t>269,79%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>125,82%</t>
+          <t>126,56%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,67; 477,16</t>
+          <t>-36,17; 505,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 446,67</t>
+          <t>-22,87; 431,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,25; 772,75</t>
+          <t>67,25; 912,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 122,85</t>
+          <t>-17,29; 118,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,41; 96,59</t>
+          <t>-26,75; 96,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,31; 199,08</t>
+          <t>25,92; 190,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 125,8</t>
+          <t>-8,53; 130,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 128,38</t>
+          <t>-12,57; 120,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,78; 234,05</t>
+          <t>56,81; 228,05</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>6,0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,89</t>
+          <t>9,84</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,87</t>
+          <t>8,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,12</t>
+          <t>0,12; 3,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,06</t>
+          <t>-0,28; 2,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 8,34</t>
+          <t>3,9; 8,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,36</t>
+          <t>-0,32; 3,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 6,24</t>
+          <t>1,43; 6,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,34; 12,87</t>
+          <t>7,09; 12,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,74</t>
+          <t>0,3; 2,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,74</t>
+          <t>0,9; 3,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,13; 9,64</t>
+          <t>6,33; 9,88</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2057,58%</t>
+          <t>2195,02%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1086,38%</t>
+          <t>1081,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1312,34%</t>
+          <t>1341,79%</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 1295,52</t>
+          <t>-45,27; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,77; 1835,12</t>
+          <t>41,21; 2168,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>334,21; 4033,17</t>
+          <t>350,7; 4289,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,34; 1401,52</t>
+          <t>-0,93; 1227,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40,2; 1865,41</t>
+          <t>63,81; 1929,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>493,39; 5638,93</t>
+          <t>478,49; 5423,81</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,98</t>
+          <t>4,35</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,32</t>
+          <t>5,98</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,76</t>
+          <t>5,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,36</t>
+          <t>-1,27; 2,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,95</t>
+          <t>-0,77; 3,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,23</t>
+          <t>1,65; 7,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 7,9</t>
+          <t>1,23; 7,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,92; 10,37</t>
+          <t>3,13; 10,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,0</t>
+          <t>3,04; 9,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,54</t>
+          <t>0,71; 4,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,05</t>
+          <t>1,95; 6,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,18</t>
+          <t>3,4; 7,67</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>406,55%</t>
+          <t>355,11%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>140,74%</t>
+          <t>194,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>219,86%</t>
+          <t>242,85%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-63,62; 508,02</t>
+          <t>-71,09; 577,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-56,52; 751,89</t>
+          <t>-52,26; 716,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59,13; 1618,79</t>
+          <t>26,9; 1450,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25,38; 420,31</t>
+          <t>19,38; 366,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>59,26; 618,96</t>
+          <t>62,89; 542,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,67; 386,92</t>
+          <t>56,15; 530,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,76; 309,12</t>
+          <t>17,23; 307,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>54,19; 423,2</t>
+          <t>58,19; 440,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>75,95; 471,58</t>
+          <t>101,92; 570,47</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,23</t>
+          <t>4,91</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>3,19</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,65</t>
+          <t>-2,14; 3,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 5,01</t>
+          <t>-1,71; 5,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 4,07</t>
+          <t>-1,75; 3,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,46; 18,36</t>
+          <t>5,38; 17,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 8,43</t>
+          <t>-1,33; 8,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 9,14</t>
+          <t>0,66; 8,76</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,82; 9,51</t>
+          <t>2,68; 9,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,26</t>
+          <t>-0,47; 5,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,1</t>
+          <t>0,84; 5,66</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-74,34; 482,74</t>
+          <t>-70,9; 418,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-61,31; 496,09</t>
+          <t>-65,84; 721,83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-47,75; 494,01</t>
+          <t>-54,2; 492,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>67,23; 556,16</t>
+          <t>55,3; 495,62</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-29,33; 254,04</t>
+          <t>-22,39; 251,13</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,52; 284,3</t>
+          <t>2,35; 292,64</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,83; 379,05</t>
+          <t>42,61; 373,16</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 192,76</t>
+          <t>-15,71; 193,27</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>16,22; 239,55</t>
+          <t>14,1; 227,67</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8,09</t>
+          <t>7,91</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,97</t>
+          <t>13,96</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10,93</t>
+          <t>10,88</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,05</t>
+          <t>-2,2; 1,11</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,38; 5,32</t>
+          <t>0,56; 5,74</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5,11; 11,14</t>
+          <t>5,32; 11,18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 4,36</t>
+          <t>-2,11; 4,12</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,01; 13,44</t>
+          <t>4,39; 12,91</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,07; 17,93</t>
+          <t>10,58; 17,73</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 2,16</t>
+          <t>-1,4; 2,04</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,17; 8,43</t>
+          <t>3,32; 8,58</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8,58; 13,24</t>
+          <t>8,64; 13,08</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>742,1%</t>
+          <t>724,86%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>553,84%</t>
+          <t>553,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>602,14%</t>
+          <t>599,07%</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 1461,33</t>
+          <t>-6,24; inf</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>178,29; 3135,84</t>
+          <t>131,32; 2946,45</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-53,38; 356,35</t>
+          <t>-57,54; 342,1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>117,64; 1172,63</t>
+          <t>80,13; 958,27</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>215,75; 1465,13</t>
+          <t>235,9; 1498,86</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-59,86; 193,76</t>
+          <t>-52,37; 185,54</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>100,18; 770,42</t>
+          <t>108,5; 764,16</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>266,52; 1368,0</t>
+          <t>296,3; 1285,7</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,55</t>
+          <t>3,52</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>8,7</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,95</t>
+          <t>6,21</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 0,64</t>
+          <t>-2,45; 0,49</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,99</t>
+          <t>0,87; 5,05</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,97</t>
+          <t>1,53; 5,95</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 0,86</t>
+          <t>-3,23; 0,86</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,93; 7,44</t>
+          <t>1,91; 7,34</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,55; 9,89</t>
+          <t>6,12; 11,15</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,16</t>
+          <t>-2,25; 0,25</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,59</t>
+          <t>2,03; 5,52</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,97; 7,09</t>
+          <t>4,51; 7,96</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>175,94%</t>
+          <t>174,62%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>151,05%</t>
+          <t>227,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>168,62%</t>
+          <t>211,74%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-80,3; 56,05</t>
+          <t>-79,93; 48,82</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>18,19; 374,21</t>
+          <t>17,64; 350,52</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>41,87; 490,49</t>
+          <t>43,64; 452,28</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-63,8; 34,74</t>
+          <t>-63,08; 38,77</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>40,09; 262,96</t>
+          <t>34,45; 260,05</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,19; 321,61</t>
+          <t>121,39; 426,99</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-63,54; 6,48</t>
+          <t>-62,35; 11,43</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>50,16; 238,26</t>
+          <t>51,77; 230,6</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>59,2; 297,59</t>
+          <t>122,21; 358,19</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,91</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>1,04</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 1,15</t>
+          <t>-2,88; 1,24</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,48; -1,38</t>
+          <t>-4,28; -1,23</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,95</t>
+          <t>-1,79; 1,78</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,59</t>
+          <t>-1,13; 4,02</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 1,91</t>
+          <t>-3,06; 1,75</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 5,38</t>
+          <t>-0,35; 4,31</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,03</t>
+          <t>-1,27; 1,89</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,2; -0,15</t>
+          <t>-3,06; -0,12</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,3</t>
+          <t>-0,56; 2,59</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-23,41%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-57,29; 43,19</t>
+          <t>-57,59; 47,75</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-88,58; -41,1</t>
+          <t>-87,84; -38,2</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-69,78; 28,43</t>
+          <t>-37,87; 63,01</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 93,5</t>
+          <t>-17,01; 79,36</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-43,52; 39,52</t>
+          <t>-42,39; 35,12</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 103,68</t>
+          <t>-4,91; 90,07</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 47,92</t>
+          <t>-21,91; 47,14</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-54,42; -3,83</t>
+          <t>-52,33; -0,88</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-40,04; 52,85</t>
+          <t>-9,85; 63,71</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2,87</t>
+          <t>3,17</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,68</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>4,33</t>
+          <t>4,75</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,74</t>
+          <t>-0,73; 0,76</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,41</t>
+          <t>-0,05; 1,4</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,78</t>
+          <t>2,35; 4,03</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,25</t>
+          <t>1,04; 3,18</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,51</t>
+          <t>2,31; 4,43</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,93</t>
+          <t>5,14; 7,3</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,79</t>
+          <t>0,48; 1,82</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,75</t>
+          <t>1,38; 2,81</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,08</t>
+          <t>4,07; 5,49</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>144,77%</t>
+          <t>159,7%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>136,4%</t>
+          <t>149,32%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>140,04%</t>
+          <t>153,61%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-27,0; 47,12</t>
+          <t>-31,25; 45,28</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 82,98</t>
+          <t>-2,85; 85,92</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>70,91; 227,68</t>
+          <t>97,49; 239,76</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>23,87; 87,31</t>
+          <t>21,14; 85,54</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>48,25; 119,9</t>
+          <t>49,66; 120,93</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>85,29; 189,49</t>
+          <t>108,94; 202,2</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>14,49; 63,92</t>
+          <t>13,58; 64,33</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>40,5; 99,83</t>
+          <t>40,86; 100,99</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>97,33; 179,57</t>
+          <t>117,5; 197,17</t>
         </is>
       </c>
     </row>
